--- a/AbbildungenDiagramme.xlsx
+++ b/AbbildungenDiagramme.xlsx
@@ -1,39 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\MyFolder\MONOTONS\GithubUVenture\UVenture-20240520_Tested1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6899D3-107A-4D87-95CF-AF884E3D6896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B95727-17B5-41C1-9E34-7D40BA22DA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{42331D4F-6DCB-4116-A52A-56045F541046}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{42331D4F-6DCB-4116-A52A-56045F541046}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
     <sheet name="Standards1000ppb_NEG" sheetId="2" r:id="rId2"/>
-    <sheet name="MSMS von Methylnitrophenol" sheetId="3" r:id="rId3"/>
+    <sheet name="MSMS von DiMethylnitrophenol" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'MSMS von Methylnitrophenol'!$A$2:$A$2074</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'MSMS von Methylnitrophenol'!$B$1</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'MSMS von Methylnitrophenol'!$B$1</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'MSMS von Methylnitrophenol'!$B$2:$B$2074</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'MSMS von Methylnitrophenol'!$A$2:$A$2074</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'MSMS von Methylnitrophenol'!$B$1</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'MSMS von Methylnitrophenol'!$B$2:$B$2074</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'MSMS von Methylnitrophenol'!$B$2:$B$2074</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'MSMS von Methylnitrophenol'!$A$2:$A$2074</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'MSMS von Methylnitrophenol'!$B$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'MSMS von Methylnitrophenol'!$B$2:$B$2074</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'MSMS von Methylnitrophenol'!$A$2:$A$2074</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'MSMS von Methylnitrophenol'!$B$1</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'MSMS von Methylnitrophenol'!$B$2:$B$2074</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'MSMS von Methylnitrophenol'!$A$2:$A$2074</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -59,7 +42,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="19">
+  <futureMetadata name="XLRICHVALUE" count="26">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -193,8 +176,57 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="19"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="20"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="21"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="23"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="24"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="25"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="19">
+  <valueMetadata count="26">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -252,12 +284,33 @@
     <bk>
       <rc t="1" v="18"/>
     </bk>
+    <bk>
+      <rc t="1" v="19"/>
+    </bk>
+    <bk>
+      <rc t="1" v="20"/>
+    </bk>
+    <bk>
+      <rc t="1" v="21"/>
+    </bk>
+    <bk>
+      <rc t="1" v="22"/>
+    </bk>
+    <bk>
+      <rc t="1" v="23"/>
+    </bk>
+    <bk>
+      <rc t="1" v="24"/>
+    </bk>
+    <bk>
+      <rc t="1" v="25"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="207">
   <si>
     <t>Ibuprofen</t>
   </si>
@@ -275,9 +328,6 @@
   </si>
   <si>
     <t>Compound</t>
-  </si>
-  <si>
-    <t>Formula</t>
   </si>
   <si>
     <t xml:space="preserve">Weight </t>
@@ -331,19 +381,10 @@
     <t>C5H7O4</t>
   </si>
   <si>
-    <t>N-Phenylmaleimide</t>
-  </si>
-  <si>
-    <t>C10H7NO2</t>
-  </si>
-  <si>
     <t>C5H7N1O5B</t>
   </si>
   <si>
     <t>BO3, C2H3N1O3B1</t>
-  </si>
-  <si>
-    <t>4-Nitro-1-Naphthol</t>
   </si>
   <si>
     <t>C10H7NO3</t>
@@ -355,19 +396,10 @@
     <t>NO</t>
   </si>
   <si>
-    <t>2-Nitro benzoic acid</t>
-  </si>
-  <si>
     <t>C7H5NO4</t>
   </si>
   <si>
     <t>C7H4N1O4</t>
-  </si>
-  <si>
-    <t>2-Nitro phenol</t>
-  </si>
-  <si>
-    <t>C₆H₅NO₃</t>
   </si>
   <si>
     <t>C6H4N1O3</t>
@@ -385,22 +417,13 @@
     <t>NO, CHNO2</t>
   </si>
   <si>
-    <t>p-Nitrophenolhydrazin</t>
-  </si>
-  <si>
     <t>C6H7N3O2</t>
   </si>
   <si>
     <t>C9H6F2</t>
   </si>
   <si>
-    <t>3-Nitrosalicylsäure</t>
-  </si>
-  <si>
     <t>C7H5NO5</t>
-  </si>
-  <si>
-    <t>28.54???</t>
   </si>
   <si>
     <t>C7H4N1O5</t>
@@ -424,25 +447,13 @@
     <t>C6H4N1O4</t>
   </si>
   <si>
-    <t>Salicylsäure</t>
-  </si>
-  <si>
     <t>C7H6O3</t>
   </si>
   <si>
     <t>C7H5O3</t>
   </si>
   <si>
-    <t>2-Sulfo-benzoesäureanhydrid</t>
-  </si>
-  <si>
-    <t>183.983032 + H2O</t>
-  </si>
-  <si>
     <t>C7H5O5S</t>
-  </si>
-  <si>
-    <t>C7H4O4S + H2O</t>
   </si>
   <si>
     <t>Syringic acid</t>
@@ -481,9 +492,6 @@
     <t>NLS</t>
   </si>
   <si>
-    <t>keine (aber schöne peak_similarity)</t>
-  </si>
-  <si>
     <t>C3H5O2</t>
   </si>
   <si>
@@ -491,36 +499,6 @@
   </si>
   <si>
     <t xml:space="preserve">NO, CHNO2, </t>
-  </si>
-  <si>
-    <r>
-      <t>NO,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> CHNO2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CO2,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> C1N1O3</t>
-    </r>
   </si>
   <si>
     <t>NO, C1H1N1O2</t>
@@ -531,16 +509,880 @@
   <si>
     <t>Intensity</t>
   </si>
+  <si>
+    <t>CH3; C2H3O</t>
+  </si>
+  <si>
+    <t>C7H5O2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   /</t>
+  </si>
+  <si>
+    <t>nf</t>
+  </si>
+  <si>
+    <t>Nitrobenzene</t>
+  </si>
+  <si>
+    <t>C6H5NO2</t>
+  </si>
+  <si>
+    <t>C6H4N1O2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  / </t>
+  </si>
+  <si>
+    <t>C7H6O2</t>
+  </si>
+  <si>
+    <t>HNO, CHNO2</t>
+  </si>
+  <si>
+    <t>Fucking breiter peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2 aber nur die masse, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   keine</t>
+  </si>
+  <si>
+    <t>CH3, C2H6, C3H6O, C4H6O2, C5H6O3</t>
+  </si>
+  <si>
+    <t>Probleme mit den isotopologue peaks. Keine wurden gefunden. nicht im MSMS oder auch nicht im Aif</t>
+  </si>
+  <si>
+    <t>4-Nitro-1-naphthol</t>
+  </si>
+  <si>
+    <t>2-Nitrobenzoic acid</t>
+  </si>
+  <si>
+    <t>2-Nitrophenol</t>
+  </si>
+  <si>
+    <t>p-Nitrophenylhydrazin</t>
+  </si>
+  <si>
+    <t>3-Nitrosalicylic acid</t>
+  </si>
+  <si>
+    <t>Salicylic acid</t>
+  </si>
+  <si>
+    <t>2-Sulfobenzoic acid</t>
+  </si>
+  <si>
+    <t>Benzoeic acid</t>
+  </si>
+  <si>
+    <t>Fragments match</t>
+  </si>
+  <si>
+    <t>0/0</t>
+  </si>
+  <si>
+    <t>0/1</t>
+  </si>
+  <si>
+    <t>1/1</t>
+  </si>
+  <si>
+    <t>xxx</t>
+  </si>
+  <si>
+    <t>2/2</t>
+  </si>
+  <si>
+    <t>2/1</t>
+  </si>
+  <si>
+    <t>0/2</t>
+  </si>
+  <si>
+    <t>1/0</t>
+  </si>
+  <si>
+    <t>1/2</t>
+  </si>
+  <si>
+    <t>nicht N-Phenylmaleimide. Irgendeine andere verbindung.</t>
+  </si>
+  <si>
+    <t>Log (peak height)</t>
+  </si>
+  <si>
+    <t>C6H5NO3</t>
+  </si>
+  <si>
+    <t>C7H6O5S</t>
+  </si>
+  <si>
+    <t>Predicted molecule formula</t>
+  </si>
+  <si>
+    <t>True formula</t>
+  </si>
+  <si>
+    <t>Neutral losses</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>HNO; CHNO2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; C2H3O</t>
+    </r>
+  </si>
+  <si>
+    <t>Acetylsalicylic acid</t>
+  </si>
+  <si>
+    <t>Phloroglucinol</t>
+  </si>
+  <si>
+    <t>4-Acetamidophenol</t>
+  </si>
+  <si>
+    <t>Pimelic acid</t>
+  </si>
+  <si>
+    <t>3´,5´-Dimethoxy-4´-hydroxyacetophenone</t>
+  </si>
+  <si>
+    <t>2-Carboxybenzaldehyde</t>
+  </si>
+  <si>
+    <t>Camphor-10-sulfonic acid</t>
+  </si>
+  <si>
+    <t>trans-Cinnamic acid</t>
+  </si>
+  <si>
+    <t>Glutaric acid</t>
+  </si>
+  <si>
+    <t>2-Iodbenzoic acid</t>
+  </si>
+  <si>
+    <t>C9H8O4</t>
+  </si>
+  <si>
+    <t>C6H6O3</t>
+  </si>
+  <si>
+    <t>C8H9NO2</t>
+  </si>
+  <si>
+    <t>C7H12O4</t>
+  </si>
+  <si>
+    <t>C10H12O4</t>
+  </si>
+  <si>
+    <t>C8H6O3</t>
+  </si>
+  <si>
+    <t>C10H16O4S</t>
+  </si>
+  <si>
+    <t>C9H8O2</t>
+  </si>
+  <si>
+    <t>C7H5IO2</t>
+  </si>
+  <si>
+    <t>C9H7O4</t>
+  </si>
+  <si>
+    <t>C6H5O3</t>
+  </si>
+  <si>
+    <t>C8H8N1O2</t>
+  </si>
+  <si>
+    <t>C7H11O4</t>
+  </si>
+  <si>
+    <t>C10H11O4</t>
+  </si>
+  <si>
+    <t>C8H5O3</t>
+  </si>
+  <si>
+    <t>C10H15O4S1</t>
+  </si>
+  <si>
+    <t>C7H4O2I1</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>C2H2O, C3H2O3</t>
+  </si>
+  <si>
+    <t>CH2, CH2O, C2H2O; C3O2</t>
+  </si>
+  <si>
+    <t>Coelution + c6h3o4 auch noch in iMSMS</t>
+  </si>
+  <si>
+    <t>Coelution + C8H6O3N</t>
+  </si>
+  <si>
+    <t>CH2, C2H4, CH2O, C2H3O, C3H3O</t>
+  </si>
+  <si>
+    <t>CO2, CH2O3, CH4O3</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NoiMSMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO, CO2, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO3Fragment, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2O, CO2, </t>
+  </si>
+  <si>
+    <t>C3H2O3, C2H2O</t>
+  </si>
+  <si>
+    <t>C3O2, C2H2</t>
+  </si>
+  <si>
+    <t>keine (Isotopo peak wurde nicht gefunden)</t>
+  </si>
+  <si>
+    <t>CO2, CH2O3, H2O</t>
+  </si>
+  <si>
+    <t>keine fragmente (I wurde nicht berücksichtigt)</t>
+  </si>
+  <si>
+    <t>3/2</t>
+  </si>
+  <si>
+    <t>0/NA</t>
+  </si>
+  <si>
+    <t>5/3</t>
+  </si>
+  <si>
+    <t>too many</t>
+  </si>
+  <si>
+    <t>C10H15O</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CO2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH2O3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H2O</t>
+    </r>
+  </si>
+  <si>
+    <t>C7H4O2</t>
+  </si>
+  <si>
+    <t>Ifragment</t>
+  </si>
+  <si>
+    <t>N-Phenylmaleimide</t>
+  </si>
+  <si>
+    <t>C10H7NO2</t>
+  </si>
+  <si>
+    <t>C7H7NO3F</t>
+  </si>
+  <si>
+    <t>PEAK LIST</t>
+  </si>
+  <si>
+    <t>JFF_ModulStandards_ESI_NEG_1000ppb_FSMSMS_11_30_90.raw</t>
+  </si>
+  <si>
+    <t>RT: 22.36 - 27.00</t>
+  </si>
+  <si>
+    <t>Number of detected peaks: 1</t>
+  </si>
+  <si>
+    <t>Apex RT</t>
+  </si>
+  <si>
+    <t>Start RT</t>
+  </si>
+  <si>
+    <t>End RT</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>%Area</t>
+  </si>
+  <si>
+    <t>%Height</t>
+  </si>
+  <si>
+    <t>Frag Masses found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  /</t>
+  </si>
+  <si>
+    <t>C3H4O2</t>
+  </si>
+  <si>
+    <t>NO, CHNO</t>
+  </si>
+  <si>
+    <t>NO, CHNO2, HNO</t>
+  </si>
+  <si>
+    <t>CO2; C2O3</t>
+  </si>
+  <si>
+    <t>CO2; C7H5O2</t>
+  </si>
+  <si>
+    <t>2/0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; C2H6; C3H6O; C4H6O2; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C5H6O3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NO; CHNO2; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HNO</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>NO; CHNO2;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HNO</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NO, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHNO</t>
+    </r>
+  </si>
+  <si>
+    <t>2/5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C3O2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C2H2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, CH2O, C2H2O</t>
+    </r>
+  </si>
+  <si>
+    <t>2/4 (3/4)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C2H4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C2H2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C2H2O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C2H3O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C3H4O1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C4H4O1</t>
+    </r>
+  </si>
+  <si>
+    <t>2/5 (7/5)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CO2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, C2O2</t>
+    </r>
+  </si>
+  <si>
+    <t>CO, CO2, C2O2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CO2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH2O3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, CH2O2, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH4O3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, H2O</t>
+    </r>
+  </si>
+  <si>
+    <t>CH2O3, CO2, CH4O3, H2O, CH2O2</t>
+  </si>
+  <si>
+    <t>Correct sum formula</t>
+  </si>
+  <si>
+    <t>Correct fragment formulas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent </t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>6.6 % (2)</t>
+  </si>
+  <si>
+    <t>Case 4</t>
+  </si>
+  <si>
+    <t>10.0 % (3)</t>
+  </si>
+  <si>
+    <t>Cumulated percent (correct)</t>
+  </si>
+  <si>
+    <t>90 %</t>
+  </si>
+  <si>
+    <t>63.3 % (19)</t>
+  </si>
+  <si>
+    <t>63 %</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -550,18 +1392,47 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -580,8 +1451,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1F0C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2D5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -589,16 +1490,352 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1160,7 +2397,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'MSMS von Methylnitrophenol'!$C$1</c:f>
+              <c:f>'MSMS von DiMethylnitrophenol'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1183,7 +2420,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'MSMS von Methylnitrophenol'!$A$2:$A$2074</c:f>
+              <c:f>'MSMS von DiMethylnitrophenol'!$A$2:$A$2074</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2073"/>
@@ -7390,7 +8627,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'MSMS von Methylnitrophenol'!$C$2:$C$2074</c:f>
+              <c:f>'MSMS von DiMethylnitrophenol'!$C$2:$C$2074</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2073"/>
@@ -15976,7 +17213,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="19">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="26">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -16053,6 +17290,34 @@
     <v>18</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>19</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>20</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>21</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>22</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>23</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>24</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>25</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -16086,6 +17351,13 @@
   <rel r:id="rId17"/>
   <rel r:id="rId18"/>
   <rel r:id="rId19"/>
+  <rel r:id="rId20"/>
+  <rel r:id="rId21"/>
+  <rel r:id="rId22"/>
+  <rel r:id="rId23"/>
+  <rel r:id="rId24"/>
+  <rel r:id="rId25"/>
+  <rel r:id="rId26"/>
 </richValueRels>
 </file>
 
@@ -16513,724 +17785,1930 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33B928F2-D98A-49CA-9FA7-466CAD446FA0}">
-  <dimension ref="B2:N20"/>
+  <dimension ref="B2:S51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-    <col min="13" max="13" width="21.85546875" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="10" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="56" customWidth="1"/>
+    <col min="17" max="17" width="13.7109375" customWidth="1"/>
+    <col min="18" max="18" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="2" spans="2:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="I2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="J2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="K2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="L2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="P2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="35">
+        <f t="shared" ref="G3:G19" si="0">LOG(Q3)</f>
+        <v>6.326916239397125</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
         <v>206.13067899999999</v>
       </c>
-      <c r="E3" s="1">
-        <f>D3-1.007825+0.000548</f>
+      <c r="J3" s="1">
+        <f>I3-1.007825+0.000548</f>
         <v>205.123402</v>
       </c>
-      <c r="F3">
+      <c r="K3">
         <v>25.18</v>
       </c>
-      <c r="G3">
+      <c r="L3" s="5">
         <v>2280994.5129999998</v>
       </c>
-      <c r="H3">
+      <c r="M3" s="5">
         <v>496807.96899999998</v>
       </c>
-      <c r="I3" t="e" vm="1">
+      <c r="N3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="O3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="Q3" s="7">
+        <v>2122835</v>
+      </c>
+      <c r="R3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="3">
-        <v>2122835</v>
-      </c>
-      <c r="M3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="36">
+        <f t="shared" si="0"/>
+        <v>6.3762217121984639</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1">
         <v>169.037509</v>
       </c>
-      <c r="E4" s="2">
-        <f t="shared" ref="E4:E5" si="0">D4-1.007825+0.00048</f>
+      <c r="J4" s="2">
+        <f t="shared" ref="J4:J5" si="1">I4-1.007825+0.00048</f>
         <v>168.03016400000001</v>
       </c>
-      <c r="F4">
+      <c r="K4">
         <v>2.88</v>
       </c>
-      <c r="G4">
+      <c r="L4" s="5">
         <v>167911.704</v>
       </c>
-      <c r="H4">
+      <c r="M4" s="5">
         <v>42392.703000000001</v>
       </c>
-      <c r="I4" t="e" vm="2">
+      <c r="N4" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>2378054</v>
+      </c>
+      <c r="R4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L4" s="3">
-        <v>2378054</v>
-      </c>
-      <c r="M4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="36">
+        <f t="shared" si="0"/>
+        <v>8.4735867412276704</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1">
         <v>116.01096</v>
       </c>
-      <c r="E5" s="2">
+      <c r="J5" s="2">
+        <f t="shared" si="1"/>
+        <v>115.003615</v>
+      </c>
+      <c r="K5">
+        <v>19.75</v>
+      </c>
+      <c r="L5" s="5">
+        <v>637379574.32099998</v>
+      </c>
+      <c r="M5" s="5">
+        <v>75431160</v>
+      </c>
+      <c r="N5" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>297568353</v>
+      </c>
+      <c r="R5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="36">
         <f t="shared" si="0"/>
-        <v>115.003615</v>
-      </c>
-      <c r="F5">
-        <v>19.75</v>
-      </c>
-      <c r="G5">
-        <v>637379574.32099998</v>
-      </c>
-      <c r="H5">
-        <v>75431160</v>
-      </c>
-      <c r="I5" t="e" vm="3">
+        <v>8.286927284738578</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>132.04226</v>
+      </c>
+      <c r="J6">
+        <v>131.03491500000001</v>
+      </c>
+      <c r="K6">
+        <v>2.38</v>
+      </c>
+      <c r="L6" s="5">
+        <v>219828393.77599999</v>
+      </c>
+      <c r="M6" s="5">
+        <v>63450476</v>
+      </c>
+      <c r="N6" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="O6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="3">
-        <v>297568353</v>
-      </c>
-      <c r="M5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>132.04226</v>
-      </c>
-      <c r="E6">
-        <v>131.03491500000001</v>
-      </c>
-      <c r="F6">
-        <v>2.38</v>
-      </c>
-      <c r="G6">
-        <v>219828393.77599999</v>
-      </c>
-      <c r="H6">
-        <v>63450476</v>
-      </c>
-      <c r="I6" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="3">
+      <c r="Q6" s="7">
         <v>193609777</v>
       </c>
-      <c r="M6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="R6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="D7">
-        <v>173.04767899999999</v>
-      </c>
-      <c r="E7">
-        <v>172.040334</v>
-      </c>
-      <c r="F7">
-        <v>1.08</v>
-      </c>
-      <c r="G7">
-        <v>475731.77100000001</v>
+      <c r="D7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="36">
+        <f t="shared" si="0"/>
+        <v>9.5325963132711404</v>
       </c>
       <c r="H7">
-        <v>160325.20300000001</v>
-      </c>
-      <c r="I7" t="e" vm="5">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>189.04259400000001</v>
+      </c>
+      <c r="J7">
+        <v>188.03524900000002</v>
+      </c>
+      <c r="K7">
+        <v>24.76</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2604630569.4050002</v>
+      </c>
+      <c r="M7" s="5">
+        <v>864726689.83000004</v>
+      </c>
+      <c r="N7" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="O7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="P7" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>3408759123</v>
+      </c>
+      <c r="R7" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="3">
-        <v>684483</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D8">
-        <v>189.04259400000001</v>
-      </c>
-      <c r="E8">
-        <v>188.03524900000002</v>
-      </c>
-      <c r="F8">
-        <v>24.76</v>
-      </c>
-      <c r="G8">
-        <v>2604630569.4050002</v>
+      <c r="E8" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="36">
+        <f t="shared" si="0"/>
+        <v>7.5188690475448414</v>
       </c>
       <c r="H8">
-        <v>864726689.83000004</v>
-      </c>
-      <c r="I8" t="e" vm="6">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>167.02185900000001</v>
+      </c>
+      <c r="J8">
+        <v>166.01451400000002</v>
+      </c>
+      <c r="K8">
+        <v>20.88</v>
+      </c>
+      <c r="L8" s="5">
+        <v>46769030.395000003</v>
+      </c>
+      <c r="M8" s="5">
+        <v>8360192.0420000004</v>
+      </c>
+      <c r="N8" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="O8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>33026994</v>
+      </c>
+      <c r="R8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="E9" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="36">
+        <f t="shared" si="0"/>
+        <v>6.882493515812512</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>139.02694399999999</v>
+      </c>
+      <c r="J9">
+        <v>138.019599</v>
+      </c>
+      <c r="K9">
+        <v>7.66</v>
+      </c>
+      <c r="L9" s="5">
+        <v>10072809.509</v>
+      </c>
+      <c r="M9" s="5">
+        <v>1948407</v>
+      </c>
+      <c r="N9" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>7629455</v>
+      </c>
+      <c r="R9" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="3">
-        <v>3408759123</v>
-      </c>
-      <c r="M8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D10" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D9">
-        <v>167.02185900000001</v>
-      </c>
-      <c r="E9">
-        <v>166.01451400000002</v>
-      </c>
-      <c r="F9">
-        <v>20.88</v>
-      </c>
-      <c r="G9">
-        <v>46769030.395000003</v>
-      </c>
-      <c r="H9">
-        <v>8360192.0420000004</v>
-      </c>
-      <c r="I9" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L9" s="3">
-        <v>33026994</v>
-      </c>
-      <c r="M9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10">
-        <v>139.02694399999999</v>
-      </c>
-      <c r="E10">
-        <v>138.019599</v>
-      </c>
-      <c r="F10">
-        <v>7.66</v>
-      </c>
-      <c r="G10">
-        <v>10072809.509</v>
+      <c r="E10" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" s="36">
+        <f t="shared" si="0"/>
+        <v>9.0585888964819343</v>
       </c>
       <c r="H10">
-        <v>1948407</v>
-      </c>
-      <c r="I10" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L10" s="3">
-        <v>7629455</v>
-      </c>
-      <c r="M10" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>153.04259400000001</v>
+      </c>
+      <c r="J10">
+        <v>152.03524900000002</v>
+      </c>
+      <c r="K10">
+        <v>17.32</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2534667559.994</v>
+      </c>
+      <c r="M10" s="5">
+        <v>318278912</v>
       </c>
       <c r="N10" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="O10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>1144429111</v>
+      </c>
+      <c r="R10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="36">
+        <f t="shared" si="0"/>
+        <v>6.4058382705130521</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
+        <v>153.05382700000001</v>
+      </c>
+      <c r="J11" s="4">
+        <v>152.04648200000003</v>
+      </c>
+      <c r="K11" s="4">
+        <v>8.31</v>
+      </c>
+      <c r="L11" s="6">
+        <v>3237836.375</v>
+      </c>
+      <c r="M11" s="6">
+        <v>696701.59400000004</v>
+      </c>
+      <c r="N11" s="4" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>2545882</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E12" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="36">
+        <f t="shared" si="0"/>
+        <v>8.966532827278515</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>183.016774</v>
+      </c>
+      <c r="J12">
+        <v>182.00942900000001</v>
+      </c>
+      <c r="K12">
+        <v>28.54</v>
+      </c>
+      <c r="L12" s="5">
+        <v>5036004825.2440004</v>
+      </c>
+      <c r="M12" s="5">
+        <v>235792128</v>
+      </c>
+      <c r="N12" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>925833364</v>
+      </c>
+      <c r="R12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>39</v>
       </c>
-      <c r="D11">
-        <v>153.04259400000001</v>
-      </c>
-      <c r="E11">
-        <v>152.03524900000002</v>
-      </c>
-      <c r="F11">
-        <v>17.32</v>
-      </c>
-      <c r="G11">
-        <v>2534667559.994</v>
-      </c>
-      <c r="H11">
-        <v>318278912</v>
-      </c>
-      <c r="I11" t="e" vm="10">
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G13" s="36">
+        <f t="shared" si="0"/>
+        <v>9.1635224316875306</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>167.058244</v>
+      </c>
+      <c r="J13">
+        <v>166.05089900000002</v>
+      </c>
+      <c r="K13">
+        <v>22.31</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1862501108.612</v>
+      </c>
+      <c r="M13" s="5">
+        <v>370189408</v>
+      </c>
+      <c r="N13" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="3" t="s">
+      <c r="O13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>1457210969</v>
+      </c>
+      <c r="R13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="36">
+        <f t="shared" si="0"/>
+        <v>6.7100756268139152</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>155.02185900000001</v>
+      </c>
+      <c r="J14">
+        <v>154.01451400000002</v>
+      </c>
+      <c r="K14">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="L14" s="5">
+        <v>287029653.07700002</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1278017.75</v>
+      </c>
+      <c r="N14" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>5129507</v>
+      </c>
+      <c r="R14" t="s">
+        <v>75</v>
+      </c>
+      <c r="S14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="G15" s="36">
+        <f t="shared" si="0"/>
+        <v>8.4425780887900039</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
+        <v>138.03169500000001</v>
+      </c>
+      <c r="J15">
+        <v>137.02435000000003</v>
+      </c>
+      <c r="K15">
+        <v>24.85</v>
+      </c>
+      <c r="L15" s="5">
+        <v>890103596.12399995</v>
+      </c>
+      <c r="M15" s="5">
+        <v>70048184</v>
+      </c>
+      <c r="N15" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>277062717</v>
+      </c>
+      <c r="R15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="0"/>
+        <v>7.5018101750201627</v>
+      </c>
+      <c r="H16">
+        <v>4</v>
+      </c>
+      <c r="I16">
+        <v>201.99359699999999</v>
+      </c>
+      <c r="J16">
+        <v>200.985772</v>
+      </c>
+      <c r="K16">
+        <v>25.67</v>
+      </c>
+      <c r="L16" s="5">
+        <v>115481259.259</v>
+      </c>
+      <c r="M16" s="5">
+        <v>8054841.5</v>
+      </c>
+      <c r="N16" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>31754858</v>
+      </c>
+      <c r="R16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="0"/>
+        <v>6.1117600537284336</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>198.05282399999999</v>
+      </c>
+      <c r="J17">
+        <v>197.045479</v>
+      </c>
+      <c r="K17">
+        <v>12.42</v>
+      </c>
+      <c r="L17" s="5">
+        <v>2068713.9750000001</v>
+      </c>
+      <c r="M17" s="5">
+        <v>305629.43800000002</v>
+      </c>
+      <c r="N17" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>1293481</v>
+      </c>
+      <c r="R17" t="s">
         <v>78</v>
       </c>
-      <c r="L11" s="3">
-        <v>1144429111</v>
-      </c>
-      <c r="M11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="4">
-        <v>153.05382700000001</v>
-      </c>
-      <c r="E12" s="4">
-        <v>152.04648200000003</v>
-      </c>
-      <c r="F12" s="4">
+    </row>
+    <row r="18" spans="2:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="G18" s="36">
+        <f t="shared" si="0"/>
+        <v>6.8440343300269966</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>182.05790999999999</v>
+      </c>
+      <c r="J18">
+        <v>181.05056500000001</v>
+      </c>
+      <c r="K18">
+        <v>12.86</v>
+      </c>
+      <c r="L18" s="5">
+        <v>10649934.002</v>
+      </c>
+      <c r="M18" s="5">
+        <v>1771064.875</v>
+      </c>
+      <c r="N18" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>6982876</v>
+      </c>
+      <c r="R18" t="s">
+        <v>79</v>
+      </c>
+      <c r="S18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="36">
+        <f t="shared" si="0"/>
+        <v>7.5846111183789384</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>152.04734500000001</v>
+      </c>
+      <c r="J19">
+        <v>151.04000000000002</v>
+      </c>
+      <c r="K19">
         <v>8.31</v>
       </c>
-      <c r="G12" s="4">
-        <v>3237836.375</v>
-      </c>
-      <c r="H12" s="4">
-        <v>696701.59400000004</v>
-      </c>
-      <c r="I12" s="4" t="e" vm="11">
+      <c r="L19" s="5">
+        <v>51001081.112000003</v>
+      </c>
+      <c r="M19" s="5">
+        <v>9718441</v>
+      </c>
+      <c r="N19" t="e" vm="18">
         <v>#VALUE!</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" s="4" t="s">
+      <c r="O19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>38424756</v>
+      </c>
+      <c r="R19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" s="36">
+        <f>LOG(Q20)</f>
+        <v>5.8960012196518763</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>172.04050000000001</v>
+      </c>
+      <c r="K20">
+        <v>24.82</v>
+      </c>
+      <c r="L20" s="10">
+        <v>644499.201</v>
+      </c>
+      <c r="M20" s="10">
+        <v>419916.21899999998</v>
+      </c>
+      <c r="N20" t="s">
+        <v>69</v>
+      </c>
+      <c r="O20" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>787048</v>
+      </c>
+      <c r="R20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="36">
+        <f>LOG(Q21)</f>
+        <v>6.9642917884890112</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>122.02468</v>
+      </c>
+      <c r="K21">
+        <v>20.84</v>
+      </c>
+      <c r="L21" s="5">
+        <v>8257053.8760000002</v>
+      </c>
+      <c r="M21" s="5">
+        <v>2945163.5</v>
+      </c>
+      <c r="N21" t="s">
+        <v>69</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>9210682</v>
+      </c>
+      <c r="R21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="G22" s="29"/>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="G23" s="29"/>
+    </row>
+    <row r="24" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="34">
+        <f>LOG(Q24)</f>
+        <v>6.247707455697932</v>
+      </c>
+      <c r="H24">
+        <v>4</v>
+      </c>
+      <c r="I24" s="23">
+        <v>180.04226</v>
+      </c>
+      <c r="J24" s="23">
+        <f>I24-1.007825+0.000548</f>
+        <v>179.03498300000001</v>
+      </c>
+      <c r="K24">
+        <v>12.41</v>
+      </c>
+      <c r="L24" s="10">
+        <v>2739261.889</v>
+      </c>
+      <c r="M24">
+        <v>415851.46899999998</v>
+      </c>
+      <c r="N24" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>1768917</v>
+      </c>
+      <c r="R24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="34">
+        <f t="shared" ref="G25:G34" si="2">LOG(Q25)</f>
+        <v>7.004721471343422</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25" s="23">
+        <v>126.031695</v>
+      </c>
+      <c r="J25" s="23">
+        <f t="shared" ref="J25:J34" si="3">I25-1.007825+0.000548</f>
+        <v>125.024418</v>
+      </c>
+      <c r="K25">
+        <v>1.9</v>
+      </c>
+      <c r="L25" s="10">
+        <v>12395545.916999999</v>
+      </c>
+      <c r="M25">
+        <v>2584084.5</v>
+      </c>
+      <c r="N25" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>10109309</v>
+      </c>
+      <c r="R25" t="s">
+        <v>138</v>
+      </c>
+      <c r="S25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="34">
+        <f t="shared" si="2"/>
+        <v>7.3197712803210759</v>
+      </c>
+      <c r="H26">
         <v>13</v>
       </c>
-      <c r="L12" s="4">
-        <v>552482</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13">
-        <v>183.016774</v>
-      </c>
-      <c r="E13">
-        <v>182.00942900000001</v>
-      </c>
-      <c r="F13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13">
-        <v>5036004825.2440004</v>
-      </c>
-      <c r="H13">
-        <v>235792128</v>
-      </c>
-      <c r="I13" t="e" vm="12">
+      <c r="I26" s="23">
+        <v>151.06332800000001</v>
+      </c>
+      <c r="J26" s="23">
+        <f t="shared" si="3"/>
+        <v>150.05605100000002</v>
+      </c>
+      <c r="K26">
+        <v>3.17</v>
+      </c>
+      <c r="L26" s="10">
+        <v>32385381.184999999</v>
+      </c>
+      <c r="M26">
+        <v>5326822</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>20881961</v>
+      </c>
+      <c r="R26" t="s">
+        <v>141</v>
+      </c>
+      <c r="S26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="G27" s="34">
+        <f t="shared" si="2"/>
+        <v>8.1476263821408157</v>
+      </c>
+      <c r="H27">
+        <v>15</v>
+      </c>
+      <c r="I27" s="23">
+        <v>160.07355999999999</v>
+      </c>
+      <c r="J27" s="23">
+        <f t="shared" si="3"/>
+        <v>159.066283</v>
+      </c>
+      <c r="K27">
+        <v>3.72</v>
+      </c>
+      <c r="L27" s="10">
+        <v>160743220.61000001</v>
+      </c>
+      <c r="M27">
+        <v>35715096</v>
+      </c>
+      <c r="N27" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L13" s="3">
-        <v>925833364</v>
-      </c>
-      <c r="M13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14">
-        <v>167.058244</v>
-      </c>
-      <c r="E14">
-        <v>166.05089900000002</v>
-      </c>
-      <c r="F14">
-        <v>22.31</v>
-      </c>
-      <c r="G14">
-        <v>1862501108.612</v>
-      </c>
-      <c r="H14">
-        <v>370189408</v>
-      </c>
-      <c r="I14" t="e" vm="13">
+      <c r="P27" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>140483844</v>
+      </c>
+      <c r="R27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="34">
+        <f t="shared" si="2"/>
+        <v>7.4337300817635272</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" s="23">
+        <v>122.03677999999999</v>
+      </c>
+      <c r="J28" s="23">
+        <f t="shared" si="3"/>
+        <v>121.02950299999999</v>
+      </c>
+      <c r="K28">
+        <v>8.91</v>
+      </c>
+      <c r="L28" s="10">
+        <v>49173960.740000002</v>
+      </c>
+      <c r="M28">
+        <v>6884552.5</v>
+      </c>
+      <c r="N28" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1457210969</v>
-      </c>
-      <c r="M14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15">
-        <v>155.02185900000001</v>
-      </c>
-      <c r="E15">
-        <v>154.01451400000002</v>
-      </c>
-      <c r="F15">
-        <v>8.4700000000000006</v>
-      </c>
-      <c r="G15">
-        <v>287029653.07700002</v>
-      </c>
-      <c r="H15">
-        <v>1278017.75</v>
-      </c>
-      <c r="I15" t="e" vm="14">
+      <c r="P28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>27147515</v>
+      </c>
+      <c r="R28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="34">
+        <f t="shared" si="2"/>
+        <v>6.1351775102481687</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" s="23">
+        <v>196.07355999999999</v>
+      </c>
+      <c r="J29" s="23">
+        <f t="shared" si="3"/>
+        <v>195.066283</v>
+      </c>
+      <c r="K29">
+        <v>16.89</v>
+      </c>
+      <c r="L29" s="10">
+        <v>1717953.9569999999</v>
+      </c>
+      <c r="M29">
+        <v>313640.125</v>
+      </c>
+      <c r="N29" t="s">
+        <v>143</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>1365141</v>
+      </c>
+      <c r="R29" t="s">
+        <v>143</v>
+      </c>
+      <c r="S29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="G30" s="34">
+        <f t="shared" si="2"/>
+        <v>8.4896234839134497</v>
+      </c>
+      <c r="H30">
+        <v>13</v>
+      </c>
+      <c r="I30" s="23">
+        <v>150.03169500000001</v>
+      </c>
+      <c r="J30" s="23">
+        <f t="shared" si="3"/>
+        <v>149.02441800000003</v>
+      </c>
+      <c r="K30">
+        <v>4.57</v>
+      </c>
+      <c r="L30" s="10">
+        <v>352702428.99400002</v>
+      </c>
+      <c r="M30">
+        <v>77741680</v>
+      </c>
+      <c r="N30" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L15" s="3">
-        <v>5129507</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16">
-        <v>138.03169500000001</v>
-      </c>
-      <c r="E16">
-        <v>137.02435000000003</v>
-      </c>
-      <c r="F16">
-        <v>24.85</v>
-      </c>
-      <c r="G16">
-        <v>890103596.12399995</v>
-      </c>
-      <c r="H16">
-        <v>70048184</v>
-      </c>
-      <c r="I16" t="e" vm="15">
+      <c r="P30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>308761743</v>
+      </c>
+      <c r="R30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="34">
+        <f t="shared" si="2"/>
+        <v>8.2923886106574951</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" s="23">
+        <v>232.076932</v>
+      </c>
+      <c r="J31" s="23">
+        <f t="shared" si="3"/>
+        <v>231.06965500000001</v>
+      </c>
+      <c r="K31">
+        <v>25.04</v>
+      </c>
+      <c r="L31" s="10">
+        <v>373097462.02399999</v>
+      </c>
+      <c r="M31">
+        <v>49912420</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q31" s="5">
+        <v>196059825</v>
+      </c>
+      <c r="R31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="G32" s="34">
+        <f t="shared" si="2"/>
+        <v>6.1135910968855844</v>
+      </c>
+      <c r="H32" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32" s="23">
+        <v>148.05242999999999</v>
+      </c>
+      <c r="J32" s="23">
+        <f t="shared" si="3"/>
+        <v>147.045153</v>
+      </c>
+      <c r="K32">
+        <v>19.32</v>
+      </c>
+      <c r="L32" s="10">
+        <v>1472693.048</v>
+      </c>
+      <c r="M32">
+        <v>262280.65600000002</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>1298946</v>
+      </c>
+      <c r="R32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" s="34">
+        <f t="shared" si="2"/>
+        <v>8.3613042206890604</v>
+      </c>
+      <c r="H33">
+        <v>8</v>
+      </c>
+      <c r="I33" s="23">
+        <v>132.04226</v>
+      </c>
+      <c r="J33" s="23">
+        <f t="shared" si="3"/>
+        <v>131.03498300000001</v>
+      </c>
+      <c r="K33">
+        <v>2.02</v>
+      </c>
+      <c r="L33" s="10">
+        <v>197856365.25299999</v>
+      </c>
+      <c r="M33">
+        <v>58430224</v>
+      </c>
+      <c r="N33" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L16" s="3">
-        <v>277062717</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17">
-        <v>200.985772</v>
-      </c>
-      <c r="F17">
-        <v>25.67</v>
-      </c>
-      <c r="G17">
-        <v>115481259.259</v>
-      </c>
-      <c r="H17">
-        <v>8054841.5</v>
-      </c>
-      <c r="I17" t="e" vm="16">
+      <c r="P33" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>229775765</v>
+      </c>
+      <c r="R33" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F34" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="G34" s="34">
+        <f t="shared" si="2"/>
+        <v>7.833803159715333</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" s="23">
+        <v>247.93343200000001</v>
+      </c>
+      <c r="J34" s="23">
+        <f t="shared" si="3"/>
+        <v>246.92615500000002</v>
+      </c>
+      <c r="K34">
+        <v>21.91</v>
+      </c>
+      <c r="L34" s="10">
+        <v>100442031.903</v>
+      </c>
+      <c r="M34">
+        <v>17201410</v>
+      </c>
+      <c r="N34" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L17" s="3">
-        <v>31754858</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18">
-        <v>198.05282399999999</v>
-      </c>
-      <c r="E18">
-        <v>197.045479</v>
-      </c>
-      <c r="F18">
-        <v>12.42</v>
-      </c>
-      <c r="G18">
-        <v>2068713.9750000001</v>
-      </c>
-      <c r="H18">
-        <v>305629.43800000002</v>
-      </c>
-      <c r="I18" t="e" vm="17">
+      <c r="P34" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>68202950</v>
+      </c>
+      <c r="R34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="18"/>
+      <c r="E41" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="I41">
+        <v>173.04767899999999</v>
+      </c>
+      <c r="J41">
+        <v>172.040334</v>
+      </c>
+      <c r="K41">
+        <v>1.08</v>
+      </c>
+      <c r="L41" s="5">
+        <v>475731.77100000001</v>
+      </c>
+      <c r="M41" s="5">
+        <v>160325.20300000001</v>
+      </c>
+      <c r="N41" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1293481</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19">
-        <v>182.05790999999999</v>
-      </c>
-      <c r="E19">
-        <v>181.05056500000001</v>
-      </c>
-      <c r="F19">
-        <v>12.86</v>
-      </c>
-      <c r="G19">
-        <v>10649934.002</v>
-      </c>
-      <c r="H19">
-        <v>1771064.875</v>
-      </c>
-      <c r="I19" t="e" vm="18">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L19" s="3">
-        <v>6982876</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20">
-        <v>152.04734500000001</v>
-      </c>
-      <c r="E20">
-        <v>151.04000000000002</v>
-      </c>
-      <c r="F20">
-        <v>8.31</v>
-      </c>
-      <c r="G20">
-        <v>51001081.112000003</v>
-      </c>
-      <c r="H20">
-        <v>9718441</v>
-      </c>
-      <c r="I20" t="e" vm="19">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L20" s="3">
-        <v>38424756</v>
-      </c>
-      <c r="M20" t="s">
-        <v>68</v>
-      </c>
+      <c r="O41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q41" s="7">
+        <v>684483</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>167</v>
+      </c>
+      <c r="M47" s="42"/>
+      <c r="N47" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="O47" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="P47" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="R47">
+        <f>19/30</f>
+        <v>0.6333333333333333</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" t="s">
+        <v>173</v>
+      </c>
+      <c r="M48" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="N48" s="45"/>
+      <c r="O48" s="45"/>
+      <c r="P48" s="46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>24.74</v>
+      </c>
+      <c r="C49">
+        <v>24.71</v>
+      </c>
+      <c r="D49" s="10">
+        <v>25.13</v>
+      </c>
+      <c r="F49" s="10">
+        <v>100</v>
+      </c>
+      <c r="H49">
+        <v>100</v>
+      </c>
+      <c r="M49" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="N49" s="45"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="46" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M50" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="N50" s="49"/>
+      <c r="O50" s="49"/>
+      <c r="P50" s="50" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" ht="48.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M51" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="N51" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="O51" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="P51" s="46"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G3:G21">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFF00"/>
+        <color theme="6" tint="0.39997558519241921"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1000000"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="20"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24:G34 G3:G21">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="&quot;6,2&quot;"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24:G34">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFF00"/>
+        <color theme="6" tint="0.39997558519241921"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -17243,13 +19721,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">

--- a/AbbildungenDiagramme.xlsx
+++ b/AbbildungenDiagramme.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\MyFolder\MONOTONS\GithubUVenture\UVenture-20240520_Tested1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B95727-17B5-41C1-9E34-7D40BA22DA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3593F18-9E6E-4C90-9549-832D315E6566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{42331D4F-6DCB-4116-A52A-56045F541046}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="14927" activeTab="2" xr2:uid="{42331D4F-6DCB-4116-A52A-56045F541046}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
     <sheet name="Standards1000ppb_NEG" sheetId="2" r:id="rId2"/>
-    <sheet name="MSMS von DiMethylnitrophenol" sheetId="3" r:id="rId3"/>
+    <sheet name="NewEval20250316" sheetId="6" r:id="rId3"/>
+    <sheet name="MSMS von DiMethylnitrophenol" sheetId="3" r:id="rId4"/>
+    <sheet name="PeakList" sheetId="4" r:id="rId5"/>
+    <sheet name="Files to analyze" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -310,7 +313,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="261">
   <si>
     <t>Ibuprofen</t>
   </si>
@@ -1371,6 +1374,345 @@
   <si>
     <t>63 %</t>
   </si>
+  <si>
+    <t>Isotopensignal von 151.04000</t>
+  </si>
+  <si>
+    <t>Keine Ahnung was?</t>
+  </si>
+  <si>
+    <t>EXISTIERT NICHT!!!</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,90</t>
+  </si>
+  <si>
+    <t>PEAK IN FSAIF_NEU_ESI.mzml</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,91</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,92</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,93</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,94</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,95</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,96</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,97</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,98</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,99</t>
+  </si>
+  <si>
+    <t>KEIN PEAK in 11,30,100</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,90</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,91</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,92</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,93</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,94</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,95</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,96</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,97</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,98</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,99</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,100</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,101</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,102</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,103</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,104</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,105</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,106</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,107</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,108</t>
+  </si>
+  <si>
+    <t>Peak in 11,30,109</t>
+  </si>
+  <si>
+    <t>JFF_ModulStandards_ESI_NEG_1000ppb_FSAIF_11_30_90</t>
+  </si>
+  <si>
+    <t>First part of the peaklist</t>
+  </si>
+  <si>
+    <t>Second part of the peaklist</t>
+  </si>
+  <si>
+    <t>JFF_Modul_Standards_neg_1000ppb_1_FSAIF_neu_ESI</t>
+  </si>
+  <si>
+    <t>C7H6NO4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CO2, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H2CO3</t>
+    </r>
+  </si>
+  <si>
+    <t>C10H6N1O3</t>
+  </si>
+  <si>
+    <t>C7H6N1O3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CO2, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CO2+NO</t>
+    </r>
+  </si>
+  <si>
+    <t>C7H5O5S1</t>
+  </si>
+  <si>
+    <t>xxxxxx</t>
+  </si>
+  <si>
+    <t>4/2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH3;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> C2H3O</t>
+    </r>
+  </si>
+  <si>
+    <t>6/3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CO2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH2O3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, CH2O2, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH4O3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, H2O, C5H8O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CO2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, C2O2, C2O3, C6H2???</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CO2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CH2O3</t>
+    </r>
+  </si>
+  <si>
+    <t>C7H4IO2</t>
+  </si>
+  <si>
+    <t>Kein Peak Matching, weil der Peak scheise aussieht.</t>
+  </si>
 </sst>
 </file>
 
@@ -1382,7 +1724,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1431,8 +1773,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1478,6 +1826,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFAE2D5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1699,7 +2053,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1835,6 +2189,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17679,7 +18039,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB24AE8F-DC48-4888-BB4C-E1F72FB68CBE}">
   <dimension ref="C2:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C2">
@@ -17785,8 +18145,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33B928F2-D98A-49CA-9FA7-466CAD446FA0}">
-  <dimension ref="B2:S51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:S51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="52.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -17796,13 +18156,13 @@
     <col min="7" max="7" width="8.85546875" style="10" customWidth="1"/>
     <col min="8" max="8" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="75.7109375" customWidth="1"/>
     <col min="16" max="16" width="56" customWidth="1"/>
     <col min="17" max="17" width="13.7109375" customWidth="1"/>
     <col min="18" max="18" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="42.8" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
@@ -17855,7 +18215,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -17910,7 +18270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>13</v>
       </c>
@@ -17965,7 +18325,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -18020,7 +18380,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -18074,7 +18434,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>81</v>
       </c>
@@ -18128,7 +18488,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>82</v>
       </c>
@@ -18182,7 +18542,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>83</v>
       </c>
@@ -18239,7 +18599,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="29.95" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>31</v>
       </c>
@@ -18293,7 +18653,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>209</v>
+      </c>
       <c r="B11" s="4" t="s">
         <v>84</v>
       </c>
@@ -18344,7 +18707,7 @@
         <v>2545882</v>
       </c>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>85</v>
       </c>
@@ -18398,7 +18761,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="29.95" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>39</v>
       </c>
@@ -18452,7 +18815,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>42</v>
       </c>
@@ -18509,7 +18872,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>86</v>
       </c>
@@ -18563,7 +18926,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>87</v>
       </c>
@@ -18617,7 +18980,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>48</v>
       </c>
@@ -18671,7 +19034,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="2:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:19" ht="60.1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>51</v>
       </c>
@@ -18728,7 +19091,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>55</v>
       </c>
@@ -18782,7 +19145,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>161</v>
       </c>
@@ -18833,7 +19196,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:19" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>70</v>
       </c>
@@ -18884,13 +19247,13 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:19" ht="15" x14ac:dyDescent="0.25">
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:19" ht="15" x14ac:dyDescent="0.25">
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:19" ht="29.95" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>109</v>
       </c>
@@ -18942,7 +19305,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="2:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:19" ht="45.1" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>110</v>
       </c>
@@ -19049,7 +19412,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="2:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:19" ht="42.8" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>112</v>
       </c>
@@ -19358,7 +19721,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:18" ht="28.55" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>117</v>
       </c>
@@ -19510,12 +19873,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="46" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="47" spans="2:18" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:18" ht="47.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>167</v>
       </c>
@@ -19534,7 +19897,7 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="48" spans="2:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:18" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>168</v>
       </c>
@@ -19565,7 +19928,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>24.74</v>
       </c>
@@ -19590,7 +19953,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="2:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" ht="16.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M50" s="48" t="s">
         <v>201</v>
       </c>
@@ -19600,7 +19963,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="51" spans="2:16" ht="48.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" ht="48.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M51" s="51" t="s">
         <v>203</v>
       </c>
@@ -19715,9 +20078,1427 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5573CC93-9807-4A94-AC45-F364E16C828D}">
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="42.8" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="35">
+        <f>LOG(L2)</f>
+        <v>5.696188553482874</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>206.13067899999999</v>
+      </c>
+      <c r="I2" s="1">
+        <f>H2-1.007825+0.000548</f>
+        <v>205.123402</v>
+      </c>
+      <c r="J2">
+        <v>25.18</v>
+      </c>
+      <c r="K2" s="5">
+        <v>2280994.5129999998</v>
+      </c>
+      <c r="L2" s="5">
+        <v>496807.96899999998</v>
+      </c>
+      <c r="M2" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="35">
+        <f t="shared" ref="F3:F20" si="0">LOG(L3)</f>
+        <v>4.6272911084898851</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1">
+        <v>169.037509</v>
+      </c>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I4" si="1">H3-1.007825+0.00048</f>
+        <v>168.03016400000001</v>
+      </c>
+      <c r="J3">
+        <v>2.88</v>
+      </c>
+      <c r="K3" s="5">
+        <v>167911.704</v>
+      </c>
+      <c r="L3" s="5">
+        <v>42392.703000000001</v>
+      </c>
+      <c r="M3" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="35">
+        <f t="shared" si="0"/>
+        <v>7.8775507864608114</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" s="1">
+        <v>116.01096</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" si="1"/>
+        <v>115.003615</v>
+      </c>
+      <c r="J4">
+        <v>19.75</v>
+      </c>
+      <c r="K4" s="5">
+        <v>637379574.32099998</v>
+      </c>
+      <c r="L4" s="5">
+        <v>75431160</v>
+      </c>
+      <c r="M4" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="28.55" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="F5" s="35">
+        <f t="shared" si="0"/>
+        <v>7.8024348844827012</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>132.04226</v>
+      </c>
+      <c r="I5">
+        <v>131.03491500000001</v>
+      </c>
+      <c r="J5">
+        <v>2.38</v>
+      </c>
+      <c r="K5" s="5">
+        <v>219828393.77599999</v>
+      </c>
+      <c r="L5" s="5">
+        <v>63450476</v>
+      </c>
+      <c r="M5" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" s="35">
+        <f t="shared" si="0"/>
+        <v>8.9368788637021268</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>189.04259400000001</v>
+      </c>
+      <c r="I6">
+        <v>188.03524900000002</v>
+      </c>
+      <c r="J6">
+        <v>24.76</v>
+      </c>
+      <c r="K6" s="5">
+        <v>2604630569.4050002</v>
+      </c>
+      <c r="L6" s="5">
+        <v>864726689.83000004</v>
+      </c>
+      <c r="M6" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="30"/>
+      <c r="F7" s="35">
+        <f t="shared" si="0"/>
+        <v>6.9222162537336294</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>167.02185900000001</v>
+      </c>
+      <c r="I7">
+        <v>166.01451400000002</v>
+      </c>
+      <c r="J7">
+        <v>20.88</v>
+      </c>
+      <c r="K7" s="5">
+        <v>46769030.395000003</v>
+      </c>
+      <c r="L7" s="5">
+        <v>8360192.0420000004</v>
+      </c>
+      <c r="M7" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="35">
+        <f t="shared" si="0"/>
+        <v>6.2896796811829967</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>139.02694399999999</v>
+      </c>
+      <c r="I8">
+        <v>138.019599</v>
+      </c>
+      <c r="J8">
+        <v>7.66</v>
+      </c>
+      <c r="K8" s="5">
+        <v>10072809.509</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1948407</v>
+      </c>
+      <c r="M8" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="42.8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="F9" s="35">
+        <f t="shared" si="0"/>
+        <v>8.5028078648056447</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>153.04259400000001</v>
+      </c>
+      <c r="I9">
+        <v>152.03524900000002</v>
+      </c>
+      <c r="J9">
+        <v>17.32</v>
+      </c>
+      <c r="K9" s="5">
+        <v>2534667559.994</v>
+      </c>
+      <c r="L9" s="5">
+        <v>318278912</v>
+      </c>
+      <c r="M9" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="35">
+        <f t="shared" si="0"/>
+        <v>5.8430468041682886</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>153.05382700000001</v>
+      </c>
+      <c r="I10" s="4">
+        <v>152.04648200000003</v>
+      </c>
+      <c r="J10" s="4">
+        <v>8.31</v>
+      </c>
+      <c r="K10" s="6">
+        <v>3237836.375</v>
+      </c>
+      <c r="L10" s="6">
+        <v>696701.59400000004</v>
+      </c>
+      <c r="M10" s="4" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.55" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="F11" s="35">
+        <f t="shared" si="0"/>
+        <v>8.372529301932822</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>183.016774</v>
+      </c>
+      <c r="I11">
+        <v>182.00942900000001</v>
+      </c>
+      <c r="J11">
+        <v>28.54</v>
+      </c>
+      <c r="K11" s="5">
+        <v>5036004825.2440004</v>
+      </c>
+      <c r="L11" s="5">
+        <v>235792128</v>
+      </c>
+      <c r="M11" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="42.8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F12" s="35">
+        <f t="shared" si="0"/>
+        <v>8.5684239883959208</v>
+      </c>
+      <c r="G12">
+        <v>6</v>
+      </c>
+      <c r="H12">
+        <v>167.058244</v>
+      </c>
+      <c r="I12">
+        <v>166.05089900000002</v>
+      </c>
+      <c r="J12">
+        <v>22.31</v>
+      </c>
+      <c r="K12" s="5">
+        <v>1862501108.612</v>
+      </c>
+      <c r="L12" s="5">
+        <v>370189408</v>
+      </c>
+      <c r="M12" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="28.55" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="35">
+        <f t="shared" si="0"/>
+        <v>6.106536885648298</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>155.02185900000001</v>
+      </c>
+      <c r="I13">
+        <v>154.01451400000002</v>
+      </c>
+      <c r="J13">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="K13" s="5">
+        <v>287029653.07700002</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1278017.75</v>
+      </c>
+      <c r="M13" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14" s="35">
+        <f t="shared" si="0"/>
+        <v>7.8453968806781491</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>138.03169500000001</v>
+      </c>
+      <c r="I14">
+        <v>137.02435000000003</v>
+      </c>
+      <c r="J14">
+        <v>24.85</v>
+      </c>
+      <c r="K14" s="5">
+        <v>890103596.12399995</v>
+      </c>
+      <c r="L14" s="5">
+        <v>70048184</v>
+      </c>
+      <c r="M14" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.55" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="F15" s="35">
+        <f t="shared" si="0"/>
+        <v>6.9060569989634759</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15">
+        <v>201.99359699999999</v>
+      </c>
+      <c r="I15">
+        <v>200.985772</v>
+      </c>
+      <c r="J15">
+        <v>25.67</v>
+      </c>
+      <c r="K15" s="5">
+        <v>115481259.259</v>
+      </c>
+      <c r="L15" s="5">
+        <v>8054841.5</v>
+      </c>
+      <c r="M15" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="35">
+        <f t="shared" si="0"/>
+        <v>5.4851951828396119</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>198.05282399999999</v>
+      </c>
+      <c r="I16">
+        <v>197.045479</v>
+      </c>
+      <c r="J16">
+        <v>12.42</v>
+      </c>
+      <c r="K16" s="5">
+        <v>2068713.9750000001</v>
+      </c>
+      <c r="L16" s="5">
+        <v>305629.43800000002</v>
+      </c>
+      <c r="M16" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="57.05" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="F17" s="35">
+        <f t="shared" si="0"/>
+        <v>6.2482344699074535</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>182.05790999999999</v>
+      </c>
+      <c r="I17">
+        <v>181.05056500000001</v>
+      </c>
+      <c r="J17">
+        <v>12.86</v>
+      </c>
+      <c r="K17" s="5">
+        <v>10649934.002</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1771064.875</v>
+      </c>
+      <c r="M17" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="28.55" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" s="35">
+        <f t="shared" si="0"/>
+        <v>6.9875966024364962</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>152.04734500000001</v>
+      </c>
+      <c r="I18">
+        <v>151.04000000000002</v>
+      </c>
+      <c r="J18">
+        <v>8.31</v>
+      </c>
+      <c r="K18" s="5">
+        <v>51001081.112000003</v>
+      </c>
+      <c r="L18" s="5">
+        <v>9718441</v>
+      </c>
+      <c r="M18" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="35">
+        <f t="shared" si="0"/>
+        <v>5.6231626493132643</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>172.04050000000001</v>
+      </c>
+      <c r="J19">
+        <v>24.82</v>
+      </c>
+      <c r="K19" s="10">
+        <v>644499.201</v>
+      </c>
+      <c r="L19" s="10">
+        <v>419916.21899999998</v>
+      </c>
+      <c r="M19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="35">
+        <f t="shared" si="0"/>
+        <v>6.4691094095396853</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>122.02468</v>
+      </c>
+      <c r="J20">
+        <v>20.84</v>
+      </c>
+      <c r="K20" s="5">
+        <v>8257053.8760000002</v>
+      </c>
+      <c r="L20" s="5">
+        <v>2945163.5</v>
+      </c>
+      <c r="M20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="29"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="29"/>
+    </row>
+    <row r="23" spans="1:13" ht="28.55" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="34">
+        <f>LOG(L23)</f>
+        <v>5.6189382399722669</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23" s="23">
+        <v>180.04226</v>
+      </c>
+      <c r="I23" s="23">
+        <f>H23-1.007825+0.000548</f>
+        <v>179.03498300000001</v>
+      </c>
+      <c r="J23">
+        <v>12.41</v>
+      </c>
+      <c r="K23" s="10">
+        <v>2739261.889</v>
+      </c>
+      <c r="L23">
+        <v>415851.46899999998</v>
+      </c>
+      <c r="M23" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="57.05" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="34">
+        <f t="shared" ref="F24:F33" si="2">LOG(L24)</f>
+        <v>6.4123067110582248</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24" s="23">
+        <v>126.031695</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" ref="I24:I33" si="3">H24-1.007825+0.000548</f>
+        <v>125.024418</v>
+      </c>
+      <c r="J24">
+        <v>1.9</v>
+      </c>
+      <c r="K24" s="10">
+        <v>12395545.916999999</v>
+      </c>
+      <c r="L24">
+        <v>2584084.5</v>
+      </c>
+      <c r="M24" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" s="34">
+        <f t="shared" si="2"/>
+        <v>6.7264681847312611</v>
+      </c>
+      <c r="G25">
+        <v>13</v>
+      </c>
+      <c r="H25" s="23">
+        <v>151.06332800000001</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="3"/>
+        <v>150.05605100000002</v>
+      </c>
+      <c r="J25">
+        <v>3.17</v>
+      </c>
+      <c r="K25" s="10">
+        <v>32385381.184999999</v>
+      </c>
+      <c r="L25">
+        <v>5326822</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="85.55" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="F26" s="34">
+        <f t="shared" si="2"/>
+        <v>7.5528518218192122</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26" s="23">
+        <v>160.07355999999999</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="3"/>
+        <v>159.066283</v>
+      </c>
+      <c r="J26">
+        <v>3.72</v>
+      </c>
+      <c r="K26" s="10">
+        <v>160743220.61000001</v>
+      </c>
+      <c r="L26">
+        <v>35715096</v>
+      </c>
+      <c r="M26" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="34">
+        <f t="shared" si="2"/>
+        <v>6.8378757161111929</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="23">
+        <v>122.03677999999999</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="3"/>
+        <v>121.02950299999999</v>
+      </c>
+      <c r="J27">
+        <v>8.91</v>
+      </c>
+      <c r="K27" s="10">
+        <v>49173960.740000002</v>
+      </c>
+      <c r="L27">
+        <v>6884552.5</v>
+      </c>
+      <c r="M27" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="34">
+        <f t="shared" si="2"/>
+        <v>5.4964316182705391</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>196.07355999999999</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="3"/>
+        <v>195.066283</v>
+      </c>
+      <c r="J28">
+        <v>16.89</v>
+      </c>
+      <c r="K28" s="10">
+        <v>1717953.9569999999</v>
+      </c>
+      <c r="L28">
+        <v>313640.125</v>
+      </c>
+      <c r="M28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="57.05" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>257</v>
+      </c>
+      <c r="F29" s="34">
+        <f t="shared" si="2"/>
+        <v>7.8906539215132314</v>
+      </c>
+      <c r="G29">
+        <v>13</v>
+      </c>
+      <c r="H29" s="23">
+        <v>150.03169500000001</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="3"/>
+        <v>149.02441800000003</v>
+      </c>
+      <c r="J29">
+        <v>4.57</v>
+      </c>
+      <c r="K29" s="10">
+        <v>352702428.99400002</v>
+      </c>
+      <c r="L29">
+        <v>77741680</v>
+      </c>
+      <c r="M29" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="28.55" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="F30" s="34">
+        <f t="shared" si="2"/>
+        <v>7.6982086271125088</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" s="23">
+        <v>232.076932</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="3"/>
+        <v>231.06965500000001</v>
+      </c>
+      <c r="J30">
+        <v>25.04</v>
+      </c>
+      <c r="K30" s="10">
+        <v>373097462.02399999</v>
+      </c>
+      <c r="L30">
+        <v>49912420</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="34">
+        <f t="shared" si="2"/>
+        <v>5.418766261226077</v>
+      </c>
+      <c r="G31" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" s="23">
+        <v>148.05242999999999</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="3"/>
+        <v>147.045153</v>
+      </c>
+      <c r="J31">
+        <v>19.32</v>
+      </c>
+      <c r="K31" s="10">
+        <v>1472693.048</v>
+      </c>
+      <c r="L31">
+        <v>262280.65600000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="28.55" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>258</v>
+      </c>
+      <c r="F32" s="34">
+        <f t="shared" si="2"/>
+        <v>7.7666375512388566</v>
+      </c>
+      <c r="G32">
+        <v>8</v>
+      </c>
+      <c r="H32" s="23">
+        <v>132.04226</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="3"/>
+        <v>131.03498300000001</v>
+      </c>
+      <c r="J32">
+        <v>2.02</v>
+      </c>
+      <c r="K32" s="10">
+        <v>197856365.25299999</v>
+      </c>
+      <c r="L32">
+        <v>58430224</v>
+      </c>
+      <c r="M32" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E33" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="F33" s="34">
+        <f t="shared" si="2"/>
+        <v>7.2355640474960028</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33" s="23">
+        <v>247.93343200000001</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="3"/>
+        <v>246.92615500000002</v>
+      </c>
+      <c r="J33">
+        <v>21.91</v>
+      </c>
+      <c r="K33" s="10">
+        <v>100442031.903</v>
+      </c>
+      <c r="L33">
+        <v>17201410</v>
+      </c>
+      <c r="M33" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F20 F23:F33">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="&quot;6,2&quot;"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F20">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFF00"/>
+        <color theme="6" tint="0.39997558519241921"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1000000"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="20"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F33">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFF00"/>
+        <color theme="6" tint="0.39997558519241921"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BED776A-D1F0-422B-8395-D21375ED2C3E}">
   <dimension ref="A1:C2067"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -44526,4 +46307,428 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6B6A560-ED87-4A9C-B620-A01FDB22DC70}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="31.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>205.123402</v>
+      </c>
+      <c r="B1">
+        <v>1510.8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>168.03016400000001</v>
+      </c>
+      <c r="B2">
+        <v>172.79999999999998</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>115.003615</v>
+      </c>
+      <c r="B3">
+        <v>1185</v>
+      </c>
+      <c r="D3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>131.03491500000001</v>
+      </c>
+      <c r="B4">
+        <v>142.79999999999998</v>
+      </c>
+      <c r="D4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>188.03524900000002</v>
+      </c>
+      <c r="B5">
+        <v>1485.6000000000001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>166.01451400000002</v>
+      </c>
+      <c r="B6">
+        <v>1252.8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>138.019599</v>
+      </c>
+      <c r="B7">
+        <v>459.6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>152.03524900000002</v>
+      </c>
+      <c r="B8">
+        <v>1039.2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>152.04648200000003</v>
+      </c>
+      <c r="B9">
+        <v>498.6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>152.04669999999999</v>
+      </c>
+      <c r="B10">
+        <v>95.4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>182.00942900000001</v>
+      </c>
+      <c r="B11">
+        <v>1712.3999999999999</v>
+      </c>
+      <c r="D11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>166.05089900000002</v>
+      </c>
+      <c r="B12">
+        <v>1338.6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>154.01451400000002</v>
+      </c>
+      <c r="B13">
+        <v>508.20000000000005</v>
+      </c>
+      <c r="D13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>137.02435000000003</v>
+      </c>
+      <c r="B14">
+        <v>1491</v>
+      </c>
+      <c r="D14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>200.985772</v>
+      </c>
+      <c r="B15">
+        <v>1540.2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>197.045479</v>
+      </c>
+      <c r="B16">
+        <v>745.2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>181.05056500000001</v>
+      </c>
+      <c r="B17">
+        <v>771.59999999999991</v>
+      </c>
+      <c r="D17" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>151.04000000000002</v>
+      </c>
+      <c r="B18">
+        <v>498.6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>172.04050000000001</v>
+      </c>
+      <c r="B19">
+        <v>1489.2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>122.02468</v>
+      </c>
+      <c r="B20">
+        <v>1250.4000000000001</v>
+      </c>
+      <c r="D20" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>179.03498300000001</v>
+      </c>
+      <c r="B22">
+        <v>744.6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>125.024418</v>
+      </c>
+      <c r="B23">
+        <v>114</v>
+      </c>
+      <c r="C23" t="s">
+        <v>212</v>
+      </c>
+      <c r="D23" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>150.05605100000002</v>
+      </c>
+      <c r="B24">
+        <v>190.2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>213</v>
+      </c>
+      <c r="D24" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>159.066283</v>
+      </c>
+      <c r="B25">
+        <v>223.20000000000002</v>
+      </c>
+      <c r="C25" t="s">
+        <v>214</v>
+      </c>
+      <c r="D25" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>121.02950299999999</v>
+      </c>
+      <c r="B26">
+        <v>534.6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>215</v>
+      </c>
+      <c r="D26" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>195.066283</v>
+      </c>
+      <c r="B27">
+        <v>1013.4000000000001</v>
+      </c>
+      <c r="C27" t="s">
+        <v>216</v>
+      </c>
+      <c r="D27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>149.02441800000003</v>
+      </c>
+      <c r="B28">
+        <v>274.20000000000005</v>
+      </c>
+      <c r="C28" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>231.06965500000001</v>
+      </c>
+      <c r="B29">
+        <v>1502.3999999999999</v>
+      </c>
+      <c r="C29" t="s">
+        <v>218</v>
+      </c>
+      <c r="D29" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>147.045153</v>
+      </c>
+      <c r="B30">
+        <v>1159.2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>219</v>
+      </c>
+      <c r="D30" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>131.03498300000001</v>
+      </c>
+      <c r="B31">
+        <v>121.2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>220</v>
+      </c>
+      <c r="D31" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>246.92615500000002</v>
+      </c>
+      <c r="B32">
+        <v>1314.6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>221</v>
+      </c>
+      <c r="D32" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49B69E2-D28D-4DB4-B4B0-16F62D10B7C1}">
+  <dimension ref="B1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>